--- a/data/censo_escolar_dataset/augmentation_method_results/censo_escolar_paraphrase_only_augmented_semantic_variation.xlsx
+++ b/data/censo_escolar_dataset/augmentation_method_results/censo_escolar_paraphrase_only_augmented_semantic_variation.xlsx
@@ -770,10 +770,10 @@
         <v>107</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.01473331617606793</v>
+        <v>0.009711610199383939</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.01261217845174994</v>
+        <v>0.008309704410859986</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -859,19 +859,19 @@
         <v>2.220446049250313e-16</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5.29171722017598e-17</v>
+        <v>3.839088963657083e-17</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>9.024064944998299e-17</v>
+        <v>8.188432136686646e-17</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>2.220446049250313e-16</v>
@@ -890,31 +890,31 @@
         <v>107</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.008009218140415886</v>
+        <v>0.001691396248553079</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1001953078016929</v>
+        <v>0.08202744208792911</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.02946663235213582</v>
+        <v>0.01942322039876784</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.02522435690349989</v>
+        <v>0.01661940882171997</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.01648765322805057</v>
+        <v>0.01348355649214333</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.01845681073990013</v>
+        <v>0.009635325114708271</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.03802877820675227</v>
+        <v>0.02439902609361694</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.04740139829101142</v>
+        <v>0.03525242579517646</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.06289255743489522</v>
+        <v>0.04839574803798237</v>
       </c>
     </row>
     <row r="13">
@@ -927,31 +927,31 @@
         <v>107</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.004004609070207943</v>
+        <v>0.0008456981242765393</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.05009765390084647</v>
+        <v>0.04101372104396456</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.01473331617606793</v>
+        <v>0.009711610199383939</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.01261217845174994</v>
+        <v>0.008309704410859986</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.00824382661402529</v>
+        <v>0.006741778246071661</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.009228405369950093</v>
+        <v>0.004817662557354191</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.01901438910337619</v>
+        <v>0.01219951304680847</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.02370069914550571</v>
+        <v>0.01762621289758823</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.03144627871744769</v>
+        <v>0.02419787401899122</v>
       </c>
     </row>
     <row r="15">
@@ -1003,16 +1003,16 @@
         <v>29</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.01627854449318465</v>
+        <v>0.01064687541165957</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.01489729319912564</v>
+        <v>0.008690774240784793</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.0263936242537581</v>
+        <v>0.01716145822019882</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.03231944605228178</v>
+        <v>0.02945097393073487</v>
       </c>
     </row>
     <row r="18">
@@ -1025,16 +1025,16 @@
         <v>46</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.01244884308174109</v>
+        <v>0.008187876206135319</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.01197624260851579</v>
+        <v>0.007154807082765002</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.01980901609760055</v>
+        <v>0.01454301597137678</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.02341665975645896</v>
+        <v>0.01558028137547751</v>
       </c>
     </row>
     <row r="19">
@@ -1047,16 +1047,16 @@
         <v>8</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.0176886226011496</v>
+        <v>0.007473769756001038</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.01258008621595572</v>
+        <v>0.005489361845177176</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.0315387731169395</v>
+        <v>0.01270360574595183</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.04081821350889298</v>
+        <v>0.01401241032596011</v>
       </c>
     </row>
     <row r="20">
@@ -1069,16 +1069,16 @@
         <v>24</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.01625963658198447</v>
+        <v>0.01224793503607171</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.01352898037847736</v>
+        <v>0.01133918387294622</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.03061652782358708</v>
+        <v>0.02302737110874456</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.03354887202899529</v>
+        <v>0.02522545451805581</v>
       </c>
     </row>
   </sheetData>
@@ -1217,19 +1217,19 @@
         <v>2.220446049250313e-16</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.273874988923439e-17</v>
+        <v>3.445519731595314e-17</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.790415108925659e-17</v>
+        <v>7.770712475854774e-17</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>2.220446049250313e-16</v>
@@ -1253,31 +1253,31 @@
         <v>29</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.008034516716607154</v>
+        <v>0.004517534252910016</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.07559742855768858</v>
+        <v>0.08202744208792911</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.03255708898636923</v>
+        <v>0.02129375082331911</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.02979458639825128</v>
+        <v>0.01738154848156959</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.01698356971182205</v>
+        <v>0.01738272011582036</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.01985931352657966</v>
+        <v>0.009346556973119369</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.04172069961787639</v>
+        <v>0.02519588328812306</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.05278724850751619</v>
+        <v>0.03432291644039746</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.06463889210456349</v>
+        <v>0.05890194786146973</v>
       </c>
     </row>
     <row r="8">
@@ -1295,31 +1295,31 @@
         <v>29</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.004017258358303577</v>
+        <v>0.002258767126455008</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.03779871427884429</v>
+        <v>0.04101372104396456</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.01627854449318465</v>
+        <v>0.01064687541165957</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.01489729319912564</v>
+        <v>0.008690774240784793</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.008491784855911023</v>
+        <v>0.008691360057910179</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.00992965676328994</v>
+        <v>0.004673278486559684</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.02086034980893819</v>
+        <v>0.01259794164406153</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.0263936242537581</v>
+        <v>0.01716145822019882</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.03231944605228178</v>
+        <v>0.02945097393073487</v>
       </c>
     </row>
     <row r="9">
@@ -1343,13 +1343,13 @@
         <v>2.220446049250313e-16</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.827056628805028e-17</v>
+        <v>3.37893964016352e-17</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.861298048323237e-17</v>
+        <v>7.975606475666614e-17</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>0</v>
@@ -1379,31 +1379,31 @@
         <v>46</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.008009218140415886</v>
+        <v>0.001691396248553079</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.04740480002929681</v>
+        <v>0.05104017376149328</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.02489768616348213</v>
+        <v>0.0163757524122706</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.02395248521703136</v>
+        <v>0.01430961416553</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.01086854377159054</v>
+        <v>0.00961424744896535</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.01584051189218214</v>
+        <v>0.01012747256229699</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.03267637776910184</v>
+        <v>0.02019052675960648</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.0396180321952011</v>
+        <v>0.02908603194275355</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.04683331951291778</v>
+        <v>0.03116056275095502</v>
       </c>
     </row>
     <row r="11">
@@ -1421,31 +1421,31 @@
         <v>46</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.004004609070207943</v>
+        <v>0.0008456981242765393</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.02370240001464841</v>
+        <v>0.02552008688074664</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.01244884308174109</v>
+        <v>0.008187876206135319</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.01197624260851579</v>
+        <v>0.007154807082765002</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.005434271885795276</v>
+        <v>0.004807123724482669</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.007920255946091068</v>
+        <v>0.005063736281148493</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.01633818888455092</v>
+        <v>0.01009526337980332</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.01980901609760055</v>
+        <v>0.01454301597137678</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.02341665975645896</v>
+        <v>0.01558028137547751</v>
       </c>
     </row>
     <row r="12">
@@ -1466,28 +1466,28 @@
         <v>0</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0</v>
+        <v>9.614813431917819e-17</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
     </row>
     <row r="13">
@@ -1505,31 +1505,31 @@
         <v>8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.01322559775357912</v>
+        <v>0.006816362067786685</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1001953078016929</v>
+        <v>0.03064242981193677</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.03537724520229919</v>
+        <v>0.01494753951200202</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.02516017243191143</v>
+        <v>0.01097872369035424</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.02741956341077981</v>
+        <v>0.008559042554828903</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.01546225501129431</v>
+        <v>0.007523334804155873</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.04367842834191094</v>
+        <v>0.02260316882279809</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.063077546233879</v>
+        <v>0.02540721149190367</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.08163642701778595</v>
+        <v>0.02802482065192021</v>
       </c>
     </row>
     <row r="14">
@@ -1547,31 +1547,31 @@
         <v>8</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.006612798876789561</v>
+        <v>0.003408181033893343</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.05009765390084647</v>
+        <v>0.01532121490596838</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.0176886226011496</v>
+        <v>0.007473769756001038</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.01258008621595572</v>
+        <v>0.005489361845177176</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.01370978170538991</v>
+        <v>0.004279521277414432</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.007731127505647153</v>
+        <v>0.00376166740207802</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.02183921417095547</v>
+        <v>0.01130158441139904</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.0315387731169395</v>
+        <v>0.01270360574595183</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.04081821350889298</v>
+        <v>0.01401241032596011</v>
       </c>
     </row>
     <row r="15">
@@ -1595,19 +1595,19 @@
         <v>2.220446049250313e-16</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>4.625929269271486e-17</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>9.064933036736789e-17</v>
+        <v>8.428844269903478e-17</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>2.220446049250313e-16</v>
@@ -1631,31 +1631,31 @@
         <v>24</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.009339295952120019</v>
+        <v>0.002216171343544904</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.07510316113797366</v>
+        <v>0.05109084798902686</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.03251927316396889</v>
+        <v>0.02449587007214337</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.02705796075695471</v>
+        <v>0.02267836774589227</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.01771719122312402</v>
+        <v>0.01376312204022117</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.01883598567150691</v>
+        <v>0.01323167702663985</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.04215537326858887</v>
+        <v>0.03501357355316284</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.06123305564717402</v>
+        <v>0.04605474221748904</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.06709774405799054</v>
+        <v>0.0504509090361116</v>
       </c>
     </row>
     <row r="17">
@@ -1673,31 +1673,31 @@
         <v>24</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.00466964797606001</v>
+        <v>0.001108085671772452</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.03755158056898683</v>
+        <v>0.02554542399451354</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.01625963658198447</v>
+        <v>0.01224793503607171</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.01352898037847736</v>
+        <v>0.01133918387294622</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.008858595611562013</v>
+        <v>0.006881561020110588</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.00941799283575355</v>
+        <v>0.006615838513319927</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.02107768663429443</v>
+        <v>0.01750678677658142</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.03061652782358708</v>
+        <v>0.02302737110874456</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.03354887202899529</v>
+        <v>0.02522545451805581</v>
       </c>
     </row>
   </sheetData>
@@ -1773,7 +1773,7 @@
         <v>107</v>
       </c>
       <c r="C6" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6" t="n">
         <v>107</v>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2026,10 +2026,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.008009218140415886</v>
+        <v>0.001691396248553079</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.004004609070207943</v>
+        <v>0.0008456981242765393</v>
       </c>
     </row>
     <row r="7">
@@ -2042,21 +2042,21 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Muito Difícil</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.008034516716607154</v>
+        <v>0.002216171343544904</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.004017258358303577</v>
+        <v>0.001108085671772452</v>
       </c>
     </row>
     <row r="8">
@@ -2069,7 +2069,7 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2080,10 +2080,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.008220675216056184</v>
+        <v>0.003677263695371025</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.004110337608028092</v>
+        <v>0.001838631847685512</v>
       </c>
     </row>
     <row r="9">
@@ -2096,7 +2096,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.008908581063061471</v>
+        <v>0.004426419614288579</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.004454290531530736</v>
+        <v>0.002213209807144401</v>
       </c>
     </row>
     <row r="10">
@@ -2123,21 +2123,21 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Muito Difícil</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.009339295952120019</v>
+        <v>0.004517534252910016</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.00466964797606001</v>
+        <v>0.002258767126455008</v>
       </c>
     </row>
     <row r="11">
@@ -2150,7 +2150,7 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.009662409870011213</v>
+        <v>0.004868531172113832</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.004831204935005606</v>
+        <v>0.002434265586056916</v>
       </c>
     </row>
     <row r="12">
@@ -2177,21 +2177,21 @@
         <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.009987116684903263</v>
+        <v>0.00562360083601976</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.004993558342451687</v>
+        <v>0.00281180041800988</v>
       </c>
     </row>
     <row r="13">
@@ -2204,21 +2204,21 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.01113969075835652</v>
+        <v>0.006139363549208854</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.005569845379178262</v>
+        <v>0.003069681774604427</v>
       </c>
     </row>
     <row r="14">
@@ -2231,7 +2231,7 @@
         <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.01183946636501332</v>
+        <v>0.006441237096312835</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.00591973318250677</v>
+        <v>0.003220618548156418</v>
       </c>
     </row>
     <row r="15">
@@ -2258,21 +2258,21 @@
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Muito Difícil</t>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.01201194984844356</v>
+        <v>0.0065847407422156</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.00600597492422178</v>
+        <v>0.0032923703711078</v>
       </c>
     </row>
     <row r="16">
@@ -2285,21 +2285,21 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.1001953078016929</v>
+        <v>0.08202744208792911</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.05009765390084647</v>
+        <v>0.04101372104396456</v>
       </c>
     </row>
     <row r="17">
@@ -2312,7 +2312,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,10 +2323,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.07559742855768858</v>
+        <v>0.06811745834206084</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.03779871427884429</v>
+        <v>0.03405872917103042</v>
       </c>
     </row>
     <row r="18">
@@ -2339,7 +2339,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.07510316113797366</v>
+        <v>0.05109084798902686</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.03755158056898683</v>
+        <v>0.02554542399451354</v>
       </c>
     </row>
     <row r="19">
@@ -2366,21 +2366,21 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.07213987709869829</v>
+        <v>0.05104017376149328</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.0360699385493492</v>
+        <v>0.02552008688074664</v>
       </c>
     </row>
     <row r="20">
@@ -2393,7 +2393,7 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2404,10 +2404,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.06712095946716023</v>
+        <v>0.05056271397631429</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03356047973358012</v>
+        <v>0.02528135698815714</v>
       </c>
     </row>
     <row r="21">
@@ -2420,7 +2420,7 @@
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.06696619007269566</v>
+        <v>0.04981734770829638</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.03348309503634794</v>
+        <v>0.02490867385414824</v>
       </c>
     </row>
     <row r="22">
@@ -2447,7 +2447,7 @@
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.05338741461336138</v>
+        <v>0.04507868214058319</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.02669370730668069</v>
+        <v>0.0225393410702916</v>
       </c>
     </row>
     <row r="23">
@@ -2474,21 +2474,21 @@
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Fácil</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.0526372069810549</v>
+        <v>0.03791684477891077</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.02631860349052745</v>
+        <v>0.01895842238945539</v>
       </c>
     </row>
     <row r="24">
@@ -2501,21 +2501,21 @@
         <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Muito Difícil</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.0515840608970809</v>
+        <v>0.0372753294056053</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.02579203044854045</v>
+        <v>0.01863766470280265</v>
       </c>
     </row>
     <row r="25">
@@ -2528,7 +2528,7 @@
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.04785574198762355</v>
+        <v>0.03678673333346882</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.02392787099381177</v>
+        <v>0.01839336666673441</v>
       </c>
     </row>
   </sheetData>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>46256.98032407407</v>
+        <v>46237.90100694444</v>
       </c>
     </row>
     <row r="7">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/home/isaquenascimento/ast-driven-data-augmentation-algorithm/data/censo_escolar_dataset/augmentation_method_results/censo_escolar_paraphrase_only_augmented.json</t>
+          <t>/home/ioolliver/Workspace/ast-driven-data-augmentation-algorithm/data/censo_escolar_dataset/augmentation_method_results/censo_escolar_paraphrase_only_augmented.json</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Qwen/Qwen3-Embedding-4B</t>
+          <t>jinaai/jina-embeddings-v3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>symmetric text similarity</t>
+          <t>text-matching</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>CC BY-NC 4.0</t>
         </is>
       </c>
     </row>
